--- a/data/trans_orig/Q5409-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q5409-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2673</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>13075</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16285</t>
+          <t>15344</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2559</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11876</t>
+          <t>12335</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14219</t>
+          <t>13417</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7843</t>
+          <t>7810</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22299</t>
+          <t>21912</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>278140</t>
+          <t>278517</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>288939</t>
+          <t>288804</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>320950</t>
+          <t>320282</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>335171</t>
+          <t>335190</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>603681</t>
+          <t>604901</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>621854</t>
+          <t>621923</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>9678</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>8456</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24847</t>
+          <t>27171</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11873</t>
+          <t>11803</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29777</t>
+          <t>30323</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14579</t>
+          <t>13892</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33384</t>
+          <t>31234</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22992</t>
+          <t>22778</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46198</t>
+          <t>45753</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>41663</t>
+          <t>42256</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>72084</t>
+          <t>69580</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>173048</t>
+          <t>173613</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>192307</t>
+          <t>192504</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>270725</t>
+          <t>269561</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>297784</t>
+          <t>298320</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>451385</t>
+          <t>452836</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>485573</t>
+          <t>484839</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,16%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11344</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13187</t>
+          <t>13532</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31630</t>
+          <t>33402</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18966</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39323</t>
+          <t>40036</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19100</t>
+          <t>19910</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38076</t>
+          <t>38990</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29389</t>
+          <t>28881</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54812</t>
+          <t>54270</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52963</t>
+          <t>52213</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84314</t>
+          <t>84147</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>458017</t>
+          <t>456812</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>478159</t>
+          <t>478663</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>599640</t>
+          <t>597355</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>629432</t>
+          <t>629313</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1063421</t>
+          <t>1064970</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1100308</t>
+          <t>1102781</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -2331,12 +2331,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9262</t>
+          <t>9981</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4242</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16596</t>
+          <t>16714</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>7654</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21580</t>
+          <t>21634</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2416,12 +2416,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17740</t>
+          <t>18639</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14781</t>
+          <t>14583</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34391</t>
+          <t>34067</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23166</t>
+          <t>22780</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47254</t>
+          <t>46131</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>286303</t>
+          <t>285794</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>302467</t>
+          <t>302603</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>309390</t>
+          <t>308563</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>331227</t>
+          <t>331545</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601814</t>
+          <t>603057</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>628929</t>
+          <t>630040</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,92%</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11734</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26660</t>
+          <t>26708</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51105</t>
+          <t>52212</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31556</t>
+          <t>30114</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>57951</t>
+          <t>58023</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24668</t>
+          <t>23794</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50264</t>
+          <t>51013</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37876</t>
+          <t>38728</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>66379</t>
+          <t>65084</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>70230</t>
+          <t>70169</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>107530</t>
+          <t>107140</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>192818</t>
+          <t>193893</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>220113</t>
+          <t>221576</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>282665</t>
+          <t>281398</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>315488</t>
+          <t>316673</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>485503</t>
+          <t>484275</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>529012</t>
+          <t>529376</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,87%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16782</t>
+          <t>17561</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35432</t>
+          <t>34891</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63460</t>
+          <t>61464</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42747</t>
+          <t>43309</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>72854</t>
+          <t>72059</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29896</t>
+          <t>32976</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59091</t>
+          <t>61720</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57386</t>
+          <t>58298</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91840</t>
+          <t>92652</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>101166</t>
+          <t>97859</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>143888</t>
+          <t>142613</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>490906</t>
+          <t>488107</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>521194</t>
+          <t>518090</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>599098</t>
+          <t>599549</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>639617</t>
+          <t>642552</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1098428</t>
+          <t>1102440</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1149976</t>
+          <t>1153699</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,57%</t>
         </is>
       </c>
     </row>
@@ -3929,12 +3929,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>950</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>7772</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14893</t>
+          <t>14908</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3979,12 +3979,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5177</t>
+          <t>5143</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18467</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -4042,12 +4042,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17221</t>
+          <t>16848</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4057,12 +4057,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18582</t>
+          <t>18763</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41026</t>
+          <t>40311</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26814</t>
+          <t>26249</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50963</t>
+          <t>50565</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4127,12 +4127,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>313303</t>
+          <t>314640</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>328383</t>
+          <t>328456</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>327837</t>
+          <t>330295</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>353096</t>
+          <t>353131</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>649734</t>
+          <t>649498</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>676290</t>
+          <t>676614</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,02%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2447</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11998</t>
+          <t>11889</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17470</t>
+          <t>16022</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41629</t>
+          <t>40028</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22542</t>
+          <t>22157</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>47128</t>
+          <t>47140</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23793</t>
+          <t>23011</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42382</t>
+          <t>42219</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4513,82 +4513,82 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>16,43%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>50009</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>36472</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>65971</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>9,11%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
           <t>16,49%</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>50009</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>36999</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>68987</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>82167</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>65552</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>102631</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>12,5%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>9,25%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>17,24%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>82167</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>65969</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>100042</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>12,5%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,62%</t>
         </is>
       </c>
     </row>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>207953</t>
+          <t>208211</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>228608</t>
+          <t>228988</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>302808</t>
+          <t>302376</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>339230</t>
+          <t>338769</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>521893</t>
+          <t>519677</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>560454</t>
+          <t>561988</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,52%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15601</t>
+          <t>15683</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22985</t>
+          <t>23425</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49509</t>
+          <t>49140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30218</t>
+          <t>29779</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>59582</t>
+          <t>58879</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -4954,12 +4954,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30442</t>
+          <t>30306</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55278</t>
+          <t>53955</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59897</t>
+          <t>60643</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98575</t>
+          <t>98122</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>99251</t>
+          <t>99459</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>142218</t>
+          <t>140034</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>527169</t>
+          <t>527034</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>553188</t>
+          <t>553530</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>642517</t>
+          <t>643084</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>687376</t>
+          <t>687257</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1180332</t>
+          <t>1182439</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1231650</t>
+          <t>1230158</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,84%</t>
         </is>
       </c>
     </row>
@@ -5522,32 +5522,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8228</t>
+          <t>8636</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5557,32 +5557,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>4511</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>8563</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5592,32 +5592,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13454</t>
+          <t>15330</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -5635,32 +5635,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23724</t>
+          <t>26663</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17104</t>
+          <t>19069</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32678</t>
+          <t>34736</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5670,32 +5670,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24300</t>
+          <t>27002</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8232</t>
+          <t>20552</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40479</t>
+          <t>34763</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5705,32 +5705,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>48023</t>
+          <t>53665</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21213</t>
+          <t>43336</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64119</t>
+          <t>65767</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -5748,32 +5748,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>340418</t>
+          <t>376042</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>331845</t>
+          <t>367392</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>348018</t>
+          <t>384024</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5783,32 +5783,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>578409</t>
+          <t>405998</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>560363</t>
+          <t>397722</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>596962</t>
+          <t>412833</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5818,32 +5818,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>918827</t>
+          <t>782041</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>899755</t>
+          <t>770427</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>950969</t>
+          <t>793331</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -5861,17 +5861,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5896,17 +5896,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>606815</t>
+          <t>437511</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>606815</t>
+          <t>437511</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>606815</t>
+          <t>437511</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>974980</t>
+          <t>844591</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>974980</t>
+          <t>844591</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>974980</t>
+          <t>844591</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5978,102 +5978,102 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12842</t>
+          <t>13319</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8392</t>
+          <t>8535</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19225</t>
+          <t>19543</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>6,33%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>39524</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>30475</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>49177</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>8,51%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>6,56%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>10,58%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>52844</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>42431</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>64893</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>6,83%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>34913</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>27692</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>44463</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>8,2%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>6,5%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>10,44%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>47755</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>39191</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>58355</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>6,75%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -6091,32 +6091,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28397</t>
+          <t>31219</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21289</t>
+          <t>23428</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37050</t>
+          <t>40934</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6126,32 +6126,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>73571</t>
+          <t>80429</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62960</t>
+          <t>68598</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>84349</t>
+          <t>93447</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6161,32 +6161,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>101968</t>
+          <t>111648</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>89241</t>
+          <t>97846</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>116894</t>
+          <t>128250</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -6204,32 +6204,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>240169</t>
+          <t>264121</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>229279</t>
+          <t>253233</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>248963</t>
+          <t>272900</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6239,32 +6239,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>317347</t>
+          <t>344656</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>304449</t>
+          <t>329936</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>329213</t>
+          <t>359078</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6274,32 +6274,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>557516</t>
+          <t>608776</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>540688</t>
+          <t>588992</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>573096</t>
+          <t>625219</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,85%</t>
         </is>
       </c>
     </row>
@@ -6317,17 +6317,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>281408</t>
+          <t>308659</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>281408</t>
+          <t>308659</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>281408</t>
+          <t>308659</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6352,17 +6352,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6387,17 +6387,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>707239</t>
+          <t>773268</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>707239</t>
+          <t>773268</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>707239</t>
+          <t>773268</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6434,32 +6434,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16865</t>
+          <t>17694</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11368</t>
+          <t>12622</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24084</t>
+          <t>25476</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6469,32 +6469,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>39019</t>
+          <t>44035</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20461</t>
+          <t>34186</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52756</t>
+          <t>56985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6504,32 +6504,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>55884</t>
+          <t>61729</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>31962</t>
+          <t>51408</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>68146</t>
+          <t>74839</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -6547,32 +6547,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>52120</t>
+          <t>57882</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42090</t>
+          <t>46594</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65131</t>
+          <t>70881</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6582,32 +6582,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>97871</t>
+          <t>107431</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56811</t>
+          <t>93849</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>126074</t>
+          <t>122872</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6617,32 +6617,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>149991</t>
+          <t>165313</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>101367</t>
+          <t>145980</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177883</t>
+          <t>186255</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -6660,32 +6660,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>580587</t>
+          <t>640162</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>566892</t>
+          <t>625117</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>592757</t>
+          <t>652826</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6695,32 +6695,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>895756</t>
+          <t>750654</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>857552</t>
+          <t>730699</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>954106</t>
+          <t>766056</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6730,32 +6730,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1476344</t>
+          <t>1390816</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1440919</t>
+          <t>1367443</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1547649</t>
+          <t>1411539</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>87,25%</t>
         </is>
       </c>
     </row>
@@ -6773,17 +6773,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>649573</t>
+          <t>715738</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>649573</t>
+          <t>715738</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>649573</t>
+          <t>715738</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6808,17 +6808,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1032646</t>
+          <t>902120</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1032646</t>
+          <t>902120</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1032646</t>
+          <t>902120</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6843,17 +6843,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1682219</t>
+          <t>1617858</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1682219</t>
+          <t>1617858</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1682219</t>
+          <t>1617858</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
